--- a/esempi/Turni_Novembre_2026.xlsx
+++ b/esempi/Turni_Novembre_2026.xlsx
@@ -1269,9 +1269,8 @@
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="str">
+      <c r="R4" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C4:$P4&lt;&gt;"")*(COUNTIFS($C4:$P4,$C4:$P4,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S4" s="3" t="str">
         <f>IF(LEN(BO4&amp;BP4&amp;BQ4&amp;BR4&amp;BS4&amp;BT4&amp;BU4&amp;BV4&amp;BW4&amp;BX4&amp;BY4&amp;BZ4&amp;CA4&amp;CB4)=0,"",LEFT(BO4&amp;BP4&amp;BQ4&amp;BR4&amp;BS4&amp;BT4&amp;BU4&amp;BV4&amp;BW4&amp;BX4&amp;BY4&amp;BZ4&amp;CA4&amp;CB4,LEN(BO4&amp;BP4&amp;BQ4&amp;BR4&amp;BS4&amp;BT4&amp;BU4&amp;BV4&amp;BW4&amp;BX4&amp;BY4&amp;BZ4&amp;CA4&amp;CB4)-2))</f>
@@ -1503,9 +1502,8 @@
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
       <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="10" t="str">
+      <c r="R5" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C5:$P5&lt;&gt;"")*(COUNTIFS($C5:$P5,$C5:$P5,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S5" s="10" t="str">
         <f>IF(LEN(BO5&amp;BP5&amp;BQ5&amp;BR5&amp;BS5&amp;BT5&amp;BU5&amp;BV5&amp;BW5&amp;BX5&amp;BY5&amp;BZ5&amp;CA5&amp;CB5)=0,"",LEFT(BO5&amp;BP5&amp;BQ5&amp;BR5&amp;BS5&amp;BT5&amp;BU5&amp;BV5&amp;BW5&amp;BX5&amp;BY5&amp;BZ5&amp;CA5&amp;CB5,LEN(BO5&amp;BP5&amp;BQ5&amp;BR5&amp;BS5&amp;BT5&amp;BU5&amp;BV5&amp;BW5&amp;BX5&amp;BY5&amp;BZ5&amp;CA5&amp;CB5)-2))</f>
@@ -1737,9 +1735,8 @@
       <c r="O6" s="10" t="n"/>
       <c r="P6" s="10" t="n"/>
       <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="str">
+      <c r="R6" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C6:$P6&lt;&gt;"")*(COUNTIFS($C6:$P6,$C6:$P6,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S6" s="10" t="str">
         <f>IF(LEN(BO6&amp;BP6&amp;BQ6&amp;BR6&amp;BS6&amp;BT6&amp;BU6&amp;BV6&amp;BW6&amp;BX6&amp;BY6&amp;BZ6&amp;CA6&amp;CB6)=0,"",LEFT(BO6&amp;BP6&amp;BQ6&amp;BR6&amp;BS6&amp;BT6&amp;BU6&amp;BV6&amp;BW6&amp;BX6&amp;BY6&amp;BZ6&amp;CA6&amp;CB6,LEN(BO6&amp;BP6&amp;BQ6&amp;BR6&amp;BS6&amp;BT6&amp;BU6&amp;BV6&amp;BW6&amp;BX6&amp;BY6&amp;BZ6&amp;CA6&amp;CB6)-2))</f>
@@ -1971,9 +1968,8 @@
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
       <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="10" t="str">
+      <c r="R7" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C7:$P7&lt;&gt;"")*(COUNTIFS($C7:$P7,$C7:$P7,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S7" s="10" t="str">
         <f>IF(LEN(BO7&amp;BP7&amp;BQ7&amp;BR7&amp;BS7&amp;BT7&amp;BU7&amp;BV7&amp;BW7&amp;BX7&amp;BY7&amp;BZ7&amp;CA7&amp;CB7)=0,"",LEFT(BO7&amp;BP7&amp;BQ7&amp;BR7&amp;BS7&amp;BT7&amp;BU7&amp;BV7&amp;BW7&amp;BX7&amp;BY7&amp;BZ7&amp;CA7&amp;CB7,LEN(BO7&amp;BP7&amp;BQ7&amp;BR7&amp;BS7&amp;BT7&amp;BU7&amp;BV7&amp;BW7&amp;BX7&amp;BY7&amp;BZ7&amp;CA7&amp;CB7)-2))</f>
@@ -2205,9 +2201,8 @@
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="str">
+      <c r="R8" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C8:$P8&lt;&gt;"")*(COUNTIFS($C8:$P8,$C8:$P8,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S8" s="10" t="str">
         <f>IF(LEN(BO8&amp;BP8&amp;BQ8&amp;BR8&amp;BS8&amp;BT8&amp;BU8&amp;BV8&amp;BW8&amp;BX8&amp;BY8&amp;BZ8&amp;CA8&amp;CB8)=0,"",LEFT(BO8&amp;BP8&amp;BQ8&amp;BR8&amp;BS8&amp;BT8&amp;BU8&amp;BV8&amp;BW8&amp;BX8&amp;BY8&amp;BZ8&amp;CA8&amp;CB8,LEN(BO8&amp;BP8&amp;BQ8&amp;BR8&amp;BS8&amp;BT8&amp;BU8&amp;BV8&amp;BW8&amp;BX8&amp;BY8&amp;BZ8&amp;CA8&amp;CB8)-2))</f>
@@ -2439,9 +2434,8 @@
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
       <c r="Q9" s="10" t="n"/>
-      <c r="R9" s="10" t="str">
+      <c r="R9" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C9:$P9&lt;&gt;"")*(COUNTIFS($C9:$P9,$C9:$P9,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S9" s="10" t="str">
         <f>IF(LEN(BO9&amp;BP9&amp;BQ9&amp;BR9&amp;BS9&amp;BT9&amp;BU9&amp;BV9&amp;BW9&amp;BX9&amp;BY9&amp;BZ9&amp;CA9&amp;CB9)=0,"",LEFT(BO9&amp;BP9&amp;BQ9&amp;BR9&amp;BS9&amp;BT9&amp;BU9&amp;BV9&amp;BW9&amp;BX9&amp;BY9&amp;BZ9&amp;CA9&amp;CB9,LEN(BO9&amp;BP9&amp;BQ9&amp;BR9&amp;BS9&amp;BT9&amp;BU9&amp;BV9&amp;BW9&amp;BX9&amp;BY9&amp;BZ9&amp;CA9&amp;CB9)-2))</f>
@@ -2673,9 +2667,8 @@
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="str">
+      <c r="R10" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C10:$P10&lt;&gt;"")*(COUNTIFS($C10:$P10,$C10:$P10,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S10" s="3" t="str">
         <f>IF(LEN(BO10&amp;BP10&amp;BQ10&amp;BR10&amp;BS10&amp;BT10&amp;BU10&amp;BV10&amp;BW10&amp;BX10&amp;BY10&amp;BZ10&amp;CA10&amp;CB10)=0,"",LEFT(BO10&amp;BP10&amp;BQ10&amp;BR10&amp;BS10&amp;BT10&amp;BU10&amp;BV10&amp;BW10&amp;BX10&amp;BY10&amp;BZ10&amp;CA10&amp;CB10,LEN(BO10&amp;BP10&amp;BQ10&amp;BR10&amp;BS10&amp;BT10&amp;BU10&amp;BV10&amp;BW10&amp;BX10&amp;BY10&amp;BZ10&amp;CA10&amp;CB10)-2))</f>
@@ -2897,9 +2890,8 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="str">
+      <c r="R11" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C11:$P11&lt;&gt;"")*(COUNTIFS($C11:$P11,$C11:$P11,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S11" s="3" t="str">
         <f>IF(LEN(BO11&amp;BP11&amp;BQ11&amp;BR11&amp;BS11&amp;BT11&amp;BU11&amp;BV11&amp;BW11&amp;BX11&amp;BY11&amp;BZ11&amp;CA11&amp;CB11)=0,"",LEFT(BO11&amp;BP11&amp;BQ11&amp;BR11&amp;BS11&amp;BT11&amp;BU11&amp;BV11&amp;BW11&amp;BX11&amp;BY11&amp;BZ11&amp;CA11&amp;CB11,LEN(BO11&amp;BP11&amp;BQ11&amp;BR11&amp;BS11&amp;BT11&amp;BU11&amp;BV11&amp;BW11&amp;BX11&amp;BY11&amp;BZ11&amp;CA11&amp;CB11)-2))</f>
@@ -3121,9 +3113,8 @@
       <c r="O12" s="10" t="n"/>
       <c r="P12" s="10" t="n"/>
       <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="10" t="str">
+      <c r="R12" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C12:$P12&lt;&gt;"")*(COUNTIFS($C12:$P12,$C12:$P12,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S12" s="10" t="str">
         <f>IF(LEN(BO12&amp;BP12&amp;BQ12&amp;BR12&amp;BS12&amp;BT12&amp;BU12&amp;BV12&amp;BW12&amp;BX12&amp;BY12&amp;BZ12&amp;CA12&amp;CB12)=0,"",LEFT(BO12&amp;BP12&amp;BQ12&amp;BR12&amp;BS12&amp;BT12&amp;BU12&amp;BV12&amp;BW12&amp;BX12&amp;BY12&amp;BZ12&amp;CA12&amp;CB12,LEN(BO12&amp;BP12&amp;BQ12&amp;BR12&amp;BS12&amp;BT12&amp;BU12&amp;BV12&amp;BW12&amp;BX12&amp;BY12&amp;BZ12&amp;CA12&amp;CB12)-2))</f>
@@ -3345,9 +3336,8 @@
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="str">
+      <c r="R13" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C13:$P13&lt;&gt;"")*(COUNTIFS($C13:$P13,$C13:$P13,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S13" s="10" t="str">
         <f>IF(LEN(BO13&amp;BP13&amp;BQ13&amp;BR13&amp;BS13&amp;BT13&amp;BU13&amp;BV13&amp;BW13&amp;BX13&amp;BY13&amp;BZ13&amp;CA13&amp;CB13)=0,"",LEFT(BO13&amp;BP13&amp;BQ13&amp;BR13&amp;BS13&amp;BT13&amp;BU13&amp;BV13&amp;BW13&amp;BX13&amp;BY13&amp;BZ13&amp;CA13&amp;CB13,LEN(BO13&amp;BP13&amp;BQ13&amp;BR13&amp;BS13&amp;BT13&amp;BU13&amp;BV13&amp;BW13&amp;BX13&amp;BY13&amp;BZ13&amp;CA13&amp;CB13)-2))</f>
@@ -3569,9 +3559,8 @@
       <c r="O14" s="10" t="n"/>
       <c r="P14" s="10" t="n"/>
       <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="10" t="str">
+      <c r="R14" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C14:$P14&lt;&gt;"")*(COUNTIFS($C14:$P14,$C14:$P14,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S14" s="10" t="str">
         <f>IF(LEN(BO14&amp;BP14&amp;BQ14&amp;BR14&amp;BS14&amp;BT14&amp;BU14&amp;BV14&amp;BW14&amp;BX14&amp;BY14&amp;BZ14&amp;CA14&amp;CB14)=0,"",LEFT(BO14&amp;BP14&amp;BQ14&amp;BR14&amp;BS14&amp;BT14&amp;BU14&amp;BV14&amp;BW14&amp;BX14&amp;BY14&amp;BZ14&amp;CA14&amp;CB14,LEN(BO14&amp;BP14&amp;BQ14&amp;BR14&amp;BS14&amp;BT14&amp;BU14&amp;BV14&amp;BW14&amp;BX14&amp;BY14&amp;BZ14&amp;CA14&amp;CB14)-2))</f>
@@ -3793,9 +3782,8 @@
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
       <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="10" t="str">
+      <c r="R15" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C15:$P15&lt;&gt;"")*(COUNTIFS($C15:$P15,$C15:$P15,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S15" s="10" t="str">
         <f>IF(LEN(BO15&amp;BP15&amp;BQ15&amp;BR15&amp;BS15&amp;BT15&amp;BU15&amp;BV15&amp;BW15&amp;BX15&amp;BY15&amp;BZ15&amp;CA15&amp;CB15)=0,"",LEFT(BO15&amp;BP15&amp;BQ15&amp;BR15&amp;BS15&amp;BT15&amp;BU15&amp;BV15&amp;BW15&amp;BX15&amp;BY15&amp;BZ15&amp;CA15&amp;CB15,LEN(BO15&amp;BP15&amp;BQ15&amp;BR15&amp;BS15&amp;BT15&amp;BU15&amp;BV15&amp;BW15&amp;BX15&amp;BY15&amp;BZ15&amp;CA15&amp;CB15)-2))</f>
@@ -4017,9 +4005,8 @@
       <c r="O16" s="10" t="n"/>
       <c r="P16" s="10" t="n"/>
       <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="10" t="str">
+      <c r="R16" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C16:$P16&lt;&gt;"")*(COUNTIFS($C16:$P16,$C16:$P16,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S16" s="10" t="str">
         <f>IF(LEN(BO16&amp;BP16&amp;BQ16&amp;BR16&amp;BS16&amp;BT16&amp;BU16&amp;BV16&amp;BW16&amp;BX16&amp;BY16&amp;BZ16&amp;CA16&amp;CB16)=0,"",LEFT(BO16&amp;BP16&amp;BQ16&amp;BR16&amp;BS16&amp;BT16&amp;BU16&amp;BV16&amp;BW16&amp;BX16&amp;BY16&amp;BZ16&amp;CA16&amp;CB16,LEN(BO16&amp;BP16&amp;BQ16&amp;BR16&amp;BS16&amp;BT16&amp;BU16&amp;BV16&amp;BW16&amp;BX16&amp;BY16&amp;BZ16&amp;CA16&amp;CB16)-2))</f>
@@ -4241,9 +4228,8 @@
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="str">
+      <c r="R17" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C17:$P17&lt;&gt;"")*(COUNTIFS($C17:$P17,$C17:$P17,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S17" s="3" t="str">
         <f>IF(LEN(BO17&amp;BP17&amp;BQ17&amp;BR17&amp;BS17&amp;BT17&amp;BU17&amp;BV17&amp;BW17&amp;BX17&amp;BY17&amp;BZ17&amp;CA17&amp;CB17)=0,"",LEFT(BO17&amp;BP17&amp;BQ17&amp;BR17&amp;BS17&amp;BT17&amp;BU17&amp;BV17&amp;BW17&amp;BX17&amp;BY17&amp;BZ17&amp;CA17&amp;CB17,LEN(BO17&amp;BP17&amp;BQ17&amp;BR17&amp;BS17&amp;BT17&amp;BU17&amp;BV17&amp;BW17&amp;BX17&amp;BY17&amp;BZ17&amp;CA17&amp;CB17)-2))</f>
@@ -4465,9 +4451,8 @@
       <c r="O18" s="3" t="n"/>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="str">
+      <c r="R18" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C18:$P18&lt;&gt;"")*(COUNTIFS($C18:$P18,$C18:$P18,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S18" s="3" t="str">
         <f>IF(LEN(BO18&amp;BP18&amp;BQ18&amp;BR18&amp;BS18&amp;BT18&amp;BU18&amp;BV18&amp;BW18&amp;BX18&amp;BY18&amp;BZ18&amp;CA18&amp;CB18)=0,"",LEFT(BO18&amp;BP18&amp;BQ18&amp;BR18&amp;BS18&amp;BT18&amp;BU18&amp;BV18&amp;BW18&amp;BX18&amp;BY18&amp;BZ18&amp;CA18&amp;CB18,LEN(BO18&amp;BP18&amp;BQ18&amp;BR18&amp;BS18&amp;BT18&amp;BU18&amp;BV18&amp;BW18&amp;BX18&amp;BY18&amp;BZ18&amp;CA18&amp;CB18)-2))</f>
@@ -4718,9 +4703,8 @@
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
       <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="str">
+      <c r="R19" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C19:$P19&lt;&gt;"")*(COUNTIFS($C19:$P19,$C19:$P19,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S19" s="10" t="str">
         <f>IF(LEN(BO19&amp;BP19&amp;BQ19&amp;BR19&amp;BS19&amp;BT19&amp;BU19&amp;BV19&amp;BW19&amp;BX19&amp;BY19&amp;BZ19&amp;CA19&amp;CB19)=0,"",LEFT(BO19&amp;BP19&amp;BQ19&amp;BR19&amp;BS19&amp;BT19&amp;BU19&amp;BV19&amp;BW19&amp;BX19&amp;BY19&amp;BZ19&amp;CA19&amp;CB19,LEN(BO19&amp;BP19&amp;BQ19&amp;BR19&amp;BS19&amp;BT19&amp;BU19&amp;BV19&amp;BW19&amp;BX19&amp;BY19&amp;BZ19&amp;CA19&amp;CB19)-2))</f>
@@ -4889,9 +4873,8 @@
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
       <c r="Q20" s="10" t="n"/>
-      <c r="R20" s="10" t="str">
+      <c r="R20" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C20:$P20&lt;&gt;"")*(COUNTIFS($C20:$P20,$C20:$P20,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S20" s="10" t="str">
         <f>IF(LEN(BO20&amp;BP20&amp;BQ20&amp;BR20&amp;BS20&amp;BT20&amp;BU20&amp;BV20&amp;BW20&amp;BX20&amp;BY20&amp;BZ20&amp;CA20&amp;CB20)=0,"",LEFT(BO20&amp;BP20&amp;BQ20&amp;BR20&amp;BS20&amp;BT20&amp;BU20&amp;BV20&amp;BW20&amp;BX20&amp;BY20&amp;BZ20&amp;CA20&amp;CB20,LEN(BO20&amp;BP20&amp;BQ20&amp;BR20&amp;BS20&amp;BT20&amp;BU20&amp;BV20&amp;BW20&amp;BX20&amp;BY20&amp;BZ20&amp;CA20&amp;CB20)-2))</f>
@@ -5065,9 +5048,8 @@
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
       <c r="Q21" s="10" t="n"/>
-      <c r="R21" s="10" t="str">
+      <c r="R21" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C21:$P21&lt;&gt;"")*(COUNTIFS($C21:$P21,$C21:$P21,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S21" s="10" t="str">
         <f>IF(LEN(BO21&amp;BP21&amp;BQ21&amp;BR21&amp;BS21&amp;BT21&amp;BU21&amp;BV21&amp;BW21&amp;BX21&amp;BY21&amp;BZ21&amp;CA21&amp;CB21)=0,"",LEFT(BO21&amp;BP21&amp;BQ21&amp;BR21&amp;BS21&amp;BT21&amp;BU21&amp;BV21&amp;BW21&amp;BX21&amp;BY21&amp;BZ21&amp;CA21&amp;CB21,LEN(BO21&amp;BP21&amp;BQ21&amp;BR21&amp;BS21&amp;BT21&amp;BU21&amp;BV21&amp;BW21&amp;BX21&amp;BY21&amp;BZ21&amp;CA21&amp;CB21)-2))</f>
@@ -5236,9 +5218,8 @@
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="10" t="n"/>
       <c r="Q22" s="10" t="n"/>
-      <c r="R22" s="10" t="str">
+      <c r="R22" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C22:$P22&lt;&gt;"")*(COUNTIFS($C22:$P22,$C22:$P22,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S22" s="10" t="str">
         <f>IF(LEN(BO22&amp;BP22&amp;BQ22&amp;BR22&amp;BS22&amp;BT22&amp;BU22&amp;BV22&amp;BW22&amp;BX22&amp;BY22&amp;BZ22&amp;CA22&amp;CB22)=0,"",LEFT(BO22&amp;BP22&amp;BQ22&amp;BR22&amp;BS22&amp;BT22&amp;BU22&amp;BV22&amp;BW22&amp;BX22&amp;BY22&amp;BZ22&amp;CA22&amp;CB22,LEN(BO22&amp;BP22&amp;BQ22&amp;BR22&amp;BS22&amp;BT22&amp;BU22&amp;BV22&amp;BW22&amp;BX22&amp;BY22&amp;BZ22&amp;CA22&amp;CB22)-2))</f>
@@ -5407,9 +5388,8 @@
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="10" t="n"/>
       <c r="Q23" s="10" t="n"/>
-      <c r="R23" s="10" t="str">
+      <c r="R23" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C23:$P23&lt;&gt;"")*(COUNTIFS($C23:$P23,$C23:$P23,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S23" s="10" t="str">
         <f>IF(LEN(BO23&amp;BP23&amp;BQ23&amp;BR23&amp;BS23&amp;BT23&amp;BU23&amp;BV23&amp;BW23&amp;BX23&amp;BY23&amp;BZ23&amp;CA23&amp;CB23)=0,"",LEFT(BO23&amp;BP23&amp;BQ23&amp;BR23&amp;BS23&amp;BT23&amp;BU23&amp;BV23&amp;BW23&amp;BX23&amp;BY23&amp;BZ23&amp;CA23&amp;CB23,LEN(BO23&amp;BP23&amp;BQ23&amp;BR23&amp;BS23&amp;BT23&amp;BU23&amp;BV23&amp;BW23&amp;BX23&amp;BY23&amp;BZ23&amp;CA23&amp;CB23)-2))</f>
@@ -5578,9 +5558,8 @@
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="str">
+      <c r="R24" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C24:$P24&lt;&gt;"")*(COUNTIFS($C24:$P24,$C24:$P24,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S24" s="3" t="str">
         <f>IF(LEN(BO24&amp;BP24&amp;BQ24&amp;BR24&amp;BS24&amp;BT24&amp;BU24&amp;BV24&amp;BW24&amp;BX24&amp;BY24&amp;BZ24&amp;CA24&amp;CB24)=0,"",LEFT(BO24&amp;BP24&amp;BQ24&amp;BR24&amp;BS24&amp;BT24&amp;BU24&amp;BV24&amp;BW24&amp;BX24&amp;BY24&amp;BZ24&amp;CA24&amp;CB24,LEN(BO24&amp;BP24&amp;BQ24&amp;BR24&amp;BS24&amp;BT24&amp;BU24&amp;BV24&amp;BW24&amp;BX24&amp;BY24&amp;BZ24&amp;CA24&amp;CB24)-2))</f>
@@ -5749,9 +5728,8 @@
       <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="str">
+      <c r="R25" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C25:$P25&lt;&gt;"")*(COUNTIFS($C25:$P25,$C25:$P25,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S25" s="3" t="str">
         <f>IF(LEN(BO25&amp;BP25&amp;BQ25&amp;BR25&amp;BS25&amp;BT25&amp;BU25&amp;BV25&amp;BW25&amp;BX25&amp;BY25&amp;BZ25&amp;CA25&amp;CB25)=0,"",LEFT(BO25&amp;BP25&amp;BQ25&amp;BR25&amp;BS25&amp;BT25&amp;BU25&amp;BV25&amp;BW25&amp;BX25&amp;BY25&amp;BZ25&amp;CA25&amp;CB25,LEN(BO25&amp;BP25&amp;BQ25&amp;BR25&amp;BS25&amp;BT25&amp;BU25&amp;BV25&amp;BW25&amp;BX25&amp;BY25&amp;BZ25&amp;CA25&amp;CB25)-2))</f>
@@ -5920,9 +5898,8 @@
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
       <c r="Q26" s="10" t="n"/>
-      <c r="R26" s="10" t="str">
+      <c r="R26" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C26:$P26&lt;&gt;"")*(COUNTIFS($C26:$P26,$C26:$P26,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S26" s="10" t="str">
         <f>IF(LEN(BO26&amp;BP26&amp;BQ26&amp;BR26&amp;BS26&amp;BT26&amp;BU26&amp;BV26&amp;BW26&amp;BX26&amp;BY26&amp;BZ26&amp;CA26&amp;CB26)=0,"",LEFT(BO26&amp;BP26&amp;BQ26&amp;BR26&amp;BS26&amp;BT26&amp;BU26&amp;BV26&amp;BW26&amp;BX26&amp;BY26&amp;BZ26&amp;CA26&amp;CB26,LEN(BO26&amp;BP26&amp;BQ26&amp;BR26&amp;BS26&amp;BT26&amp;BU26&amp;BV26&amp;BW26&amp;BX26&amp;BY26&amp;BZ26&amp;CA26&amp;CB26)-2))</f>
@@ -6091,9 +6068,8 @@
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
       <c r="Q27" s="10" t="n"/>
-      <c r="R27" s="10" t="str">
+      <c r="R27" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C27:$P27&lt;&gt;"")*(COUNTIFS($C27:$P27,$C27:$P27,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S27" s="10" t="str">
         <f>IF(LEN(BO27&amp;BP27&amp;BQ27&amp;BR27&amp;BS27&amp;BT27&amp;BU27&amp;BV27&amp;BW27&amp;BX27&amp;BY27&amp;BZ27&amp;CA27&amp;CB27)=0,"",LEFT(BO27&amp;BP27&amp;BQ27&amp;BR27&amp;BS27&amp;BT27&amp;BU27&amp;BV27&amp;BW27&amp;BX27&amp;BY27&amp;BZ27&amp;CA27&amp;CB27,LEN(BO27&amp;BP27&amp;BQ27&amp;BR27&amp;BS27&amp;BT27&amp;BU27&amp;BV27&amp;BW27&amp;BX27&amp;BY27&amp;BZ27&amp;CA27&amp;CB27)-2))</f>
@@ -6262,9 +6238,8 @@
       <c r="O28" s="10" t="n"/>
       <c r="P28" s="10" t="n"/>
       <c r="Q28" s="10" t="n"/>
-      <c r="R28" s="10" t="str">
+      <c r="R28" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C28:$P28&lt;&gt;"")*(COUNTIFS($C28:$P28,$C28:$P28,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S28" s="10" t="str">
         <f>IF(LEN(BO28&amp;BP28&amp;BQ28&amp;BR28&amp;BS28&amp;BT28&amp;BU28&amp;BV28&amp;BW28&amp;BX28&amp;BY28&amp;BZ28&amp;CA28&amp;CB28)=0,"",LEFT(BO28&amp;BP28&amp;BQ28&amp;BR28&amp;BS28&amp;BT28&amp;BU28&amp;BV28&amp;BW28&amp;BX28&amp;BY28&amp;BZ28&amp;CA28&amp;CB28,LEN(BO28&amp;BP28&amp;BQ28&amp;BR28&amp;BS28&amp;BT28&amp;BU28&amp;BV28&amp;BW28&amp;BX28&amp;BY28&amp;BZ28&amp;CA28&amp;CB28)-2))</f>
@@ -6433,9 +6408,8 @@
       <c r="O29" s="10" t="n"/>
       <c r="P29" s="10" t="n"/>
       <c r="Q29" s="10" t="n"/>
-      <c r="R29" s="10" t="str">
+      <c r="R29" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C29:$P29&lt;&gt;"")*(COUNTIFS($C29:$P29,$C29:$P29,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S29" s="10" t="str">
         <f>IF(LEN(BO29&amp;BP29&amp;BQ29&amp;BR29&amp;BS29&amp;BT29&amp;BU29&amp;BV29&amp;BW29&amp;BX29&amp;BY29&amp;BZ29&amp;CA29&amp;CB29)=0,"",LEFT(BO29&amp;BP29&amp;BQ29&amp;BR29&amp;BS29&amp;BT29&amp;BU29&amp;BV29&amp;BW29&amp;BX29&amp;BY29&amp;BZ29&amp;CA29&amp;CB29,LEN(BO29&amp;BP29&amp;BQ29&amp;BR29&amp;BS29&amp;BT29&amp;BU29&amp;BV29&amp;BW29&amp;BX29&amp;BY29&amp;BZ29&amp;CA29&amp;CB29)-2))</f>
@@ -6604,9 +6578,8 @@
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
       <c r="Q30" s="10" t="n"/>
-      <c r="R30" s="10" t="str">
+      <c r="R30" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C30:$P30&lt;&gt;"")*(COUNTIFS($C30:$P30,$C30:$P30,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S30" s="10" t="str">
         <f>IF(LEN(BO30&amp;BP30&amp;BQ30&amp;BR30&amp;BS30&amp;BT30&amp;BU30&amp;BV30&amp;BW30&amp;BX30&amp;BY30&amp;BZ30&amp;CA30&amp;CB30)=0,"",LEFT(BO30&amp;BP30&amp;BQ30&amp;BR30&amp;BS30&amp;BT30&amp;BU30&amp;BV30&amp;BW30&amp;BX30&amp;BY30&amp;BZ30&amp;CA30&amp;CB30,LEN(BO30&amp;BP30&amp;BQ30&amp;BR30&amp;BS30&amp;BT30&amp;BU30&amp;BV30&amp;BW30&amp;BX30&amp;BY30&amp;BZ30&amp;CA30&amp;CB30)-2))</f>
@@ -6775,9 +6748,8 @@
       <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n"/>
-      <c r="R31" s="3" t="str">
+      <c r="R31" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C31:$P31&lt;&gt;"")*(COUNTIFS($C31:$P31,$C31:$P31,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S31" s="3" t="str">
         <f>IF(LEN(BO31&amp;BP31&amp;BQ31&amp;BR31&amp;BS31&amp;BT31&amp;BU31&amp;BV31&amp;BW31&amp;BX31&amp;BY31&amp;BZ31&amp;CA31&amp;CB31)=0,"",LEFT(BO31&amp;BP31&amp;BQ31&amp;BR31&amp;BS31&amp;BT31&amp;BU31&amp;BV31&amp;BW31&amp;BX31&amp;BY31&amp;BZ31&amp;CA31&amp;CB31,LEN(BO31&amp;BP31&amp;BQ31&amp;BR31&amp;BS31&amp;BT31&amp;BU31&amp;BV31&amp;BW31&amp;BX31&amp;BY31&amp;BZ31&amp;CA31&amp;CB31)-2))</f>
@@ -6946,9 +6918,8 @@
       <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="str">
+      <c r="R32" s="3">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C32:$P32&lt;&gt;"")*(COUNTIFS($C32:$P32,$C32:$P32,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S32" s="3" t="str">
         <f>IF(LEN(BO32&amp;BP32&amp;BQ32&amp;BR32&amp;BS32&amp;BT32&amp;BU32&amp;BV32&amp;BW32&amp;BX32&amp;BY32&amp;BZ32&amp;CA32&amp;CB32)=0,"",LEFT(BO32&amp;BP32&amp;BQ32&amp;BR32&amp;BS32&amp;BT32&amp;BU32&amp;BV32&amp;BW32&amp;BX32&amp;BY32&amp;BZ32&amp;CA32&amp;CB32,LEN(BO32&amp;BP32&amp;BQ32&amp;BR32&amp;BS32&amp;BT32&amp;BU32&amp;BV32&amp;BW32&amp;BX32&amp;BY32&amp;BZ32&amp;CA32&amp;CB32)-2))</f>
@@ -7117,9 +7088,8 @@
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
       <c r="Q33" s="10" t="n"/>
-      <c r="R33" s="10" t="str">
+      <c r="R33" s="10">
         <f>IF(SUMPRODUCT(($C$3:$P$3&lt;&gt;"")*($C33:$P33&lt;&gt;"")*(COUNTIFS($C33:$P33,$C33:$P33,$C$3:$P$3,$C$3:$P$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="S33" s="10" t="str">
         <f>IF(LEN(BO33&amp;BP33&amp;BQ33&amp;BR33&amp;BS33&amp;BT33&amp;BU33&amp;BV33&amp;BW33&amp;BX33&amp;BY33&amp;BZ33&amp;CA33&amp;CB33)=0,"",LEFT(BO33&amp;BP33&amp;BQ33&amp;BR33&amp;BS33&amp;BT33&amp;BU33&amp;BV33&amp;BW33&amp;BX33&amp;BY33&amp;BZ33&amp;CA33&amp;CB33,LEN(BO33&amp;BP33&amp;BQ33&amp;BR33&amp;BS33&amp;BT33&amp;BU33&amp;BV33&amp;BW33&amp;BX33&amp;BY33&amp;BZ33&amp;CA33&amp;CB33)-2))</f>
